--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4310344827586207</v>
+        <v>0.2876712328767123</v>
       </c>
       <c r="B2">
-        <v>0.1081081081081081</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5285714285714286</v>
+        <v>0.3943661971830986</v>
       </c>
       <c r="D2">
-        <v>0.6947368421052632</v>
+        <v>0.8037383177570093</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2876712328767123</v>
+        <v>0.2597402597402597</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="C2">
-        <v>0.3943661971830986</v>
+        <v>0.3661971830985916</v>
       </c>
       <c r="D2">
-        <v>0.8037383177570093</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="E2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F2">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
